--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96666</v>
+        <v>96669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96656</v>
+        <v>96659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96450</v>
+        <v>96453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98196</v>
+        <v>98199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96669</v>
+        <v>96670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96659</v>
+        <v>96660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96453</v>
+        <v>96454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96453</v>
+        <v>96454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98199</v>
+        <v>98200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96670</v>
+        <v>96675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77869</v>
+        <v>77871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77869</v>
+        <v>77871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
+        <v>96665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96649</v>
+        <v>96654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96454</v>
+        <v>96459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96454</v>
+        <v>96459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>136192201</v>
       </c>
       <c r="B10" t="n">
-        <v>83444</v>
+        <v>83446</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>136191497</v>
       </c>
       <c r="B11" t="n">
-        <v>79730</v>
+        <v>79732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98200</v>
+        <v>98205</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>136191869</v>
       </c>
       <c r="B13" t="n">
-        <v>81137</v>
+        <v>81139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>136192731</v>
       </c>
       <c r="B14" t="n">
-        <v>81137</v>
+        <v>81139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136192041</v>
       </c>
       <c r="B3" t="n">
-        <v>77871</v>
+        <v>77865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136192274</v>
       </c>
       <c r="B4" t="n">
-        <v>77871</v>
+        <v>77865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2202-2026 artfynd.xlsx
+++ b/artfynd/S 2202-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136192425</v>
       </c>
       <c r="B2" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>136191414</v>
       </c>
       <c r="B6" t="n">
-        <v>96665</v>
+        <v>96667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>136192184</v>
       </c>
       <c r="B7" t="n">
-        <v>96654</v>
+        <v>96656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>136191740</v>
       </c>
       <c r="B8" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>136192452</v>
       </c>
       <c r="B9" t="n">
-        <v>96459</v>
+        <v>96461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>136192690</v>
       </c>
       <c r="B12" t="n">
-        <v>98205</v>
+        <v>98207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
